--- a/figures/figures_data/agingConditionCount.xlsx
+++ b/figures/figures_data/agingConditionCount.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A541"/>
+  <dimension ref="A1:A534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,142 +437,142 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -582,7 +582,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -592,7 +592,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -602,12 +602,12 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -617,32 +617,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -652,57 +652,57 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -722,7 +722,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -737,7 +737,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -757,7 +757,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -767,27 +767,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -822,7 +822,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -832,7 +832,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -852,12 +852,12 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -867,12 +867,12 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -882,7 +882,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -917,82 +917,82 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -1007,12 +1007,12 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -1117,42 +1117,42 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -1397,12 +1397,12 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -1417,17 +1417,17 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -1457,17 +1457,17 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209">
@@ -1477,7 +1477,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211">
@@ -1487,12 +1487,12 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -1502,7 +1502,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -1512,12 +1512,12 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
@@ -1527,7 +1527,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
@@ -1547,7 +1547,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -1592,17 +1592,17 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -1617,77 +1617,77 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -1697,7 +1697,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -1712,7 +1712,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="258">
@@ -1727,7 +1727,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -1777,7 +1777,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -1797,7 +1797,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="275">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -1892,7 +1892,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -2262,12 +2262,12 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
@@ -2277,47 +2277,47 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -2662,27 +2662,27 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -2692,7 +2692,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -2802,47 +2802,47 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="484">
@@ -2887,32 +2887,32 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -2922,12 +2922,12 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503">
@@ -2947,57 +2947,57 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="515">
@@ -3007,42 +3007,42 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -3052,87 +3052,52 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
